--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.98915878288917</v>
+        <v>7.798238302219491</v>
       </c>
       <c r="D2" t="n">
-        <v>47.96357690247629</v>
+        <v>7.794081246652397</v>
       </c>
       <c r="E2" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F2" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.467998491936</v>
+        <v>9.6635497549396</v>
       </c>
       <c r="D3" t="n">
-        <v>59.61181440918534</v>
+        <v>9.686919841492619</v>
       </c>
       <c r="E3" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F3" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.66213966468325</v>
+        <v>5.957597695511029</v>
       </c>
       <c r="D4" t="n">
-        <v>36.68195375017405</v>
+        <v>5.960817484403282</v>
       </c>
       <c r="E4" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F4" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.95953744716451</v>
+        <v>5.518424835164232</v>
       </c>
       <c r="D5" t="n">
-        <v>33.86306230219054</v>
+        <v>5.502747624105962</v>
       </c>
       <c r="E5" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F5" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.74642595373938</v>
+        <v>10.84629421748265</v>
       </c>
       <c r="D6" t="n">
-        <v>66.27085088192187</v>
+        <v>10.7690132683123</v>
       </c>
       <c r="E6" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F6" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.95354659227339</v>
+        <v>8.767451321244426</v>
       </c>
       <c r="D7" t="n">
-        <v>54.73676791269008</v>
+        <v>8.894724785812137</v>
       </c>
       <c r="E7" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F7" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.46503227227444</v>
+        <v>4.788067744244597</v>
       </c>
       <c r="D8" t="n">
-        <v>28.9240271162296</v>
+        <v>4.70015440638731</v>
       </c>
       <c r="E8" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F8" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.78997390718322</v>
+        <v>6.953370759917274</v>
       </c>
       <c r="D9" t="n">
-        <v>42.16760186169229</v>
+        <v>6.852235302524997</v>
       </c>
       <c r="E9" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F9" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.86758061345867</v>
+        <v>1.765981849687033</v>
       </c>
       <c r="D10" t="n">
-        <v>11.22698325621469</v>
+        <v>1.824384779134887</v>
       </c>
       <c r="E10" t="n">
-        <v>16.03711480818682</v>
+        <v>2.606031156330359</v>
       </c>
       <c r="F10" t="n">
-        <v>16.01457280588151</v>
+        <v>2.602368080955745</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
